--- a/DataAnalysis/TryingToPackStuffBetter/PreprocessingRTandDIM/LT/0.05/Results.xlsx
+++ b/DataAnalysis/TryingToPackStuffBetter/PreprocessingRTandDIM/LT/0.05/Results.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Utente\Desktop\CultureAwarenessTest\DataAnalysis\TryingToPackStuffBetter\PreprocessingRTandDIM\LT\0.05\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0BB5589D-E045-4745-AB8A-A952E6B71387}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{29EE6A52-99C6-4D32-90E0-43FC2D0AD042}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -165,8 +165,9 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="2" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normale" xfId="0" builtinId="0"/>
@@ -486,34 +487,34 @@
       <c r="A3" t="s">
         <v>3</v>
       </c>
-      <c r="C3">
+      <c r="C3" s="1">
         <v>34.233333333333334</v>
       </c>
-      <c r="D3">
+      <c r="D3" s="1">
         <v>4.7316059893122233</v>
       </c>
-      <c r="E3">
+      <c r="E3" s="1">
         <v>31.3</v>
       </c>
-      <c r="F3">
+      <c r="F3" s="1">
         <v>4.4231533677101549</v>
       </c>
-      <c r="G3">
+      <c r="G3" s="1">
         <v>12.333333333333334</v>
       </c>
-      <c r="H3">
+      <c r="H3" s="1">
         <v>2.2334044054078626</v>
       </c>
-      <c r="I3">
+      <c r="I3" s="1">
         <v>25.955555555555563</v>
       </c>
-      <c r="J3">
+      <c r="J3" s="1">
         <v>2.6431002319206196</v>
       </c>
-      <c r="K3">
+      <c r="K3" s="1">
         <v>13.622222222222218</v>
       </c>
-      <c r="L3">
+      <c r="L3" s="1">
         <v>2.345602662825041</v>
       </c>
     </row>
@@ -521,34 +522,34 @@
       <c r="A4" t="s">
         <v>2</v>
       </c>
-      <c r="C4">
+      <c r="C4" s="1">
         <v>32.833333333333336</v>
       </c>
-      <c r="D4">
+      <c r="D4" s="1">
         <v>3.9218557317872396</v>
       </c>
-      <c r="E4">
+      <c r="E4" s="1">
         <v>30.966666666666665</v>
       </c>
-      <c r="F4">
+      <c r="F4" s="1">
         <v>3.4972778529811439</v>
       </c>
-      <c r="G4">
+      <c r="G4" s="1">
         <v>10.833333333333334</v>
       </c>
-      <c r="H4">
+      <c r="H4" s="1">
         <v>2.9378482569650148</v>
       </c>
-      <c r="I4">
+      <c r="I4" s="1">
         <v>24.877777777777776</v>
       </c>
-      <c r="J4">
+      <c r="J4" s="1">
         <v>2.5130348018568931</v>
       </c>
-      <c r="K4">
+      <c r="K4" s="1">
         <v>14.044444444444446</v>
       </c>
-      <c r="L4">
+      <c r="L4" s="1">
         <v>2.1661782111192989</v>
       </c>
     </row>
@@ -556,34 +557,34 @@
       <c r="A5" t="s">
         <v>27</v>
       </c>
-      <c r="C5">
+      <c r="C5" s="1">
         <v>28.571428571428573</v>
       </c>
-      <c r="D5">
+      <c r="D5" s="1">
         <v>3.1547394428670152</v>
       </c>
-      <c r="E5">
+      <c r="E5" s="1">
         <v>27.5</v>
       </c>
-      <c r="F5">
+      <c r="F5" s="1">
         <v>4.5460605656619517</v>
       </c>
-      <c r="G5">
+      <c r="G5" s="1">
         <v>9.4285714285714288</v>
       </c>
-      <c r="H5">
+      <c r="H5" s="1">
         <v>1.9023794624226815</v>
       </c>
-      <c r="I5">
+      <c r="I5" s="1">
         <v>21.833333333333332</v>
       </c>
-      <c r="J5">
+      <c r="J5" s="1">
         <v>2.52945609729607</v>
       </c>
-      <c r="K5">
+      <c r="K5" s="1">
         <v>12.404761904761907</v>
       </c>
-      <c r="L5">
+      <c r="L5" s="1">
         <v>2.0042943314782344</v>
       </c>
     </row>
@@ -591,39 +592,49 @@
       <c r="A6" t="s">
         <v>27</v>
       </c>
+      <c r="C6" s="1"/>
+      <c r="D6" s="1"/>
+      <c r="E6" s="1"/>
+      <c r="F6" s="1"/>
+      <c r="G6" s="1"/>
+      <c r="H6" s="1"/>
+      <c r="I6" s="1"/>
+      <c r="J6" s="1"/>
+      <c r="K6" s="1"/>
+      <c r="L6" s="1"/>
     </row>
     <row r="7" spans="1:12" x14ac:dyDescent="0.3">
       <c r="B7" t="s">
         <v>28</v>
       </c>
-      <c r="C7">
+      <c r="C7" s="1">
         <v>30.75</v>
       </c>
-      <c r="D7">
+      <c r="D7" s="1">
         <v>2.7156951228000539</v>
       </c>
-      <c r="E7">
+      <c r="E7" s="1">
         <v>29.166666666666668</v>
       </c>
-      <c r="F7">
+      <c r="F7" s="1">
         <v>3.6009258068816976</v>
       </c>
-      <c r="G7">
+      <c r="G7" s="1">
         <v>9.1666666666666661</v>
       </c>
-      <c r="H7">
+      <c r="H7" s="1">
         <v>1.9916492328386197</v>
       </c>
-      <c r="I7">
+      <c r="I7" s="1">
         <v>23.027777777777775</v>
       </c>
-      <c r="J7">
+      <c r="J7" s="1">
         <v>1.6713822179616842</v>
       </c>
-      <c r="K7">
+      <c r="K7" s="1">
         <v>13.861111111111109</v>
       </c>
-      <c r="L7">
+      <c r="L7" s="1">
         <v>1.0023121418149286</v>
       </c>
     </row>
